--- a/results/final_20260514_v2_summary/Yeast_PartialAbstention_summary.xlsx
+++ b/results/final_20260514_v2_summary/Yeast_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.6837±0.0148</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.6781±0.0159</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.6590±0.0174</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.6008±0.0146</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.8197±0.0053</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.8291±0.0046</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.8437±0.0054</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.8643±0.0043</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.7058±0.0086</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.7016±0.0068</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.6910±0.0094</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.6526±0.0129</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.6777±0.0111</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.6910±0.0114</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.7132±0.0122</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.7394±0.0107</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.6671±0.0063</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.6706±0.0052</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.6759±0.0079</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.6666±0.0086</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.8158±0.0052</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.8178±0.0046</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.8141±0.0051</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.7873±0.0060</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5688±0.0079</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5729±0.0069</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.5792±0.0092</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.5692±0.0096</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.4194±0.0121</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.4237±0.0116</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.4344±0.0115</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.4466±0.0111</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6155±0.0505</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.5824±0.0474</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5331±0.0342</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.4398±0.0200</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.4133±0.0095</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.4235±0.0086</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.4440±0.0088</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.4853±0.0123</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9999±0.0004</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9998±0.0006</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.9941±0.0042</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.6855±0.0074</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.6932±0.0062</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.7034±0.0079</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.7038±0.0064</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.7058±0.0105</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.7016±0.0078</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.6878±0.0105</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.6488±0.0111</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.6665±0.0121</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.6852±0.0111</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.7199±0.0106</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7692±0.0085</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.2445±0.0202</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.2381±0.0219</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.2319±0.0187</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.2128±0.0192</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.2445±0.0202</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.2381±0.0219</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.2319±0.0188</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.2106±0.0192</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.6813±0.0136</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6763±0.0146</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6541±0.0177</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.5963±0.0148</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.8190±0.0060</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.8272±0.0050</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.8416±0.0056</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.8619±0.0046</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6951±0.0103</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6914±0.0088</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0092</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6461±0.0129</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.7024±0.0113</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.7054±0.0112</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.7228±0.0120</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7449±0.0103</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.6749±0.0066</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.6733±0.0066</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.6763±0.0080</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6652±0.0088</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.8149±0.0060</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.8158±0.0052</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.8115±0.0053</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.7836±0.0067</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.5759±0.0083</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.5744±0.0087</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.5783±0.0097</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.5662±0.0100</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.4310±0.0124</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.4298±0.0108</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.4397±0.0121</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.4482±0.0125</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6239±0.0307</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.5738±0.0418</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.5100±0.0330</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.4327±0.0212</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.4349±0.0111</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.4374±0.0085</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.4556±0.0095</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.4930±0.0133</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9997±0.0007</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.9944±0.0042</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6920±0.0083</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6953±0.0070</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.7035±0.0079</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.7019±0.0072</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6939±0.0121</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6911±0.0095</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6788±0.0103</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6413±0.0115</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6903±0.0129</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6998±0.0109</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.7301±0.0110</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7755±0.0084</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.2404±0.0203</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.2285±0.0230</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.2196±0.0193</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.2022±0.0181</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.2404±0.0203</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.2285±0.0230</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.2195±0.0194</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.2000±0.0180</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.6826±0.0143</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.6778±0.0158</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.6584±0.0174</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.6002±0.0137</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.8194±0.0052</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.8291±0.0046</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.8438±0.0055</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.8641±0.0044</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.7047±0.0085</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.7016±0.0071</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.6910±0.0093</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.6520±0.0132</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.6777±0.0101</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.6911±0.0114</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.7133±0.0118</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.7393±0.0109</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.6669±0.0062</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.6707±0.0053</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.6760±0.0077</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.6663±0.0090</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.8156±0.0052</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.8178±0.0047</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.8141±0.0052</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.7869±0.0063</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5686±0.0080</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5730±0.0071</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.5792±0.0093</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.5687±0.0099</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.4197±0.0120</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.4241±0.0117</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.4350±0.0114</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.4466±0.0115</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.6149±0.0496</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.5862±0.0469</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.5321±0.0357</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.4397±0.0203</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.4138±0.0090</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.4237±0.0088</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.4444±0.0084</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.4854±0.0123</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9999±0.0004</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9996±0.0008</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.9941±0.0042</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6853±0.0073</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.6933±0.0064</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.7035±0.0079</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.7034±0.0068</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.7050±0.0104</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.7017±0.0079</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.6878±0.0106</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.6482±0.0114</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.6669±0.0116</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.6853±0.0112</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.7200±0.0105</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.7691±0.0087</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.2449±0.0205</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.2386±0.0222</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.2319±0.0191</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.2118±0.0182</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.2449±0.0205</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.2386±0.0222</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.2319±0.0192</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.2095±0.0183</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.6817±0.0128</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.6763±0.0145</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.6539±0.0179</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.5957±0.0139</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.8185±0.0059</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.8271±0.0052</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.8414±0.0056</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.8616±0.0047</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.6945±0.0100</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.6911±0.0091</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.6825±0.0092</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.6452±0.0131</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.7019±0.0108</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.7057±0.0109</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.7231±0.0119</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.7453±0.0104</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.6744±0.0061</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.6732±0.0066</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.6763±0.0080</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.6648±0.0091</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.8145±0.0058</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.8157±0.0054</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.8114±0.0053</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.7831±0.0070</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.5753±0.0076</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.5742±0.0088</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.5782±0.0098</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.5655±0.0103</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.4302±0.0120</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.4297±0.0107</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.4399±0.0119</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.4482±0.0125</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.6232±0.0312</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.5726±0.0422</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.5087±0.0320</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.4320±0.0211</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.4345±0.0105</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.4375±0.0083</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.4560±0.0094</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.4934±0.0131</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9997±0.0007</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.9944±0.0045</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.6913±0.0079</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.6952±0.0072</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.7034±0.0081</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.7013±0.0075</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.6931±0.0117</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.6909±0.0097</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.6785±0.0103</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.6402±0.0116</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.6898±0.0123</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.6998±0.0109</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.7303±0.0111</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.7755±0.0085</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.2404±0.0193</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.2281±0.0233</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.2193±0.0197</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.2006±0.0176</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.2404±0.0193</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.2281±0.0233</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.2192±0.0197</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.1983±0.0176</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.7457±0.0119</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.7462±0.0126</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.7250±0.0135</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.6729±0.0142</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.8130±0.0040</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.8100±0.0038</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.8037±0.0043</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.7857±0.0041</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.7330±0.0085</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.7273±0.0073</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.7097±0.0071</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.6628±0.0096</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.6002±0.0129</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.5986±0.0127</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.6048±0.0140</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.6231±0.0115</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.6319±0.0076</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.6289±0.0070</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.6270±0.0075</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.6177±0.0064</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.8130±0.0040</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.8100±0.0038</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.8036±0.0043</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.7853±0.0041</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.5295±0.0075</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.5245±0.0073</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.5200±0.0087</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.5024±0.0076</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.3792±0.0082</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.3717±0.0083</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.3740±0.0117</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.3839±0.0095</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.6453±0.0625</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.6227±0.0627</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.5639±0.0501</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.4602±0.0328</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.3516±0.0080</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.3479±0.0086</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.3559±0.0109</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.3790±0.0092</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.9952±0.0053</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.6574±0.0072</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.6528±0.0066</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.6479±0.0081</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.6344±0.0057</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.7377±0.0077</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.7302±0.0075</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.7084±0.0070</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.6552±0.0092</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.5930±0.0132</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.5905±0.0125</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.5972±0.0151</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.6150±0.0113</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.2003±0.0158</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.1854±0.0200</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.1701±0.0180</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.1247±0.0176</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.2003±0.0158</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.1854±0.0200</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.1701±0.0180</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.1247±0.0176</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.6905±0.0142</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.6768±0.0147</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.6327±0.0186</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.5428±0.0248</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.8045±0.0050</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.7973±0.0069</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.7748±0.0064</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.7102±0.0072</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.6767±0.0085</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.6601±0.0124</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.6172±0.0096</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.5240±0.0105</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.7001±0.0115</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.7127±0.0105</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.7412±0.0104</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.7877±0.0096</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.6664±0.0052</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.6631±0.0084</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.6507±0.0070</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.6073±0.0073</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.8044±0.0050</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.7971±0.0069</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.7743±0.0064</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.7087±0.0072</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.5636±0.0059</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.5559±0.0098</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.5327±0.0092</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.4701±0.0088</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.4251±0.0092</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.4282±0.0113</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.4388±0.0095</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.4423±0.0070</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.5842±0.0321</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.5450±0.0350</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.4520±0.0209</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.3701±0.0095</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.4375±0.0093</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.4516±0.0086</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.4896±0.0098</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.5631±0.0104</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9999±0.0004</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.9998±0.0007</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.9982±0.0024</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.6806±0.0060</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.6767±0.0087</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.6625±0.0073</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.6192±0.0071</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.6728±0.0091</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.6537±0.0131</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.6057±0.0098</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.5133±0.0102</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.6887±0.0115</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.7016±0.0102</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.7311±0.0120</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.7805±0.0095</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.2131±0.0197</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.1777±0.0200</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.1076±0.0154</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.0210±0.0087</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.2131±0.0197</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.1777±0.0200</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.1076±0.0154</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0210±0.0087</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.7760±0.0117</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.7728±0.0122</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.7495±0.0133</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.6842±0.0146</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.8102±0.0045</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.8078±0.0037</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.8024±0.0045</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.7847±0.0044</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.7407±0.0067</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.7355±0.0083</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.7178±0.0067</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.6682±0.0091</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.5714±0.0146</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.5731±0.0133</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.5819±0.0141</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.6022±0.0128</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.6164±0.0091</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.6156±0.0079</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.6159±0.0081</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.6084±0.0068</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.8102±0.0044</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.8078±0.0037</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.8022±0.0045</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.7842±0.0044</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.5127±0.0096</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.5089±0.0076</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.5071±0.0090</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.4922±0.0078</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.3604±0.0093</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.3555±0.0075</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.3606±0.0114</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.3745±0.0096</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.6264±0.0681</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.6166±0.0611</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.5675±0.0474</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.4588±0.0293</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.3289±0.0085</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.3273±0.0079</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.3369±0.0105</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.3627±0.0102</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.9949±0.0064</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.6438±0.0085</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.6406±0.0068</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.6375±0.0084</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.6254±0.0063</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.7453±0.0060</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.7378±0.0081</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.7159±0.0063</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.6597±0.0087</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.5669±0.0142</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.5662±0.0119</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.5748±0.0146</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.5947±0.0126</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.1796±0.0146</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.1627±0.0156</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.1532±0.0175</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.1177±0.0150</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.1796±0.0146</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.1627±0.0156</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.1532±0.0175</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.1177±0.0150</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.6908±0.0157</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.6772±0.0147</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.6322±0.0189</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.5414±0.0242</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.8050±0.0051</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.7972±0.0069</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.7750±0.0065</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.7106±0.0072</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.6777±0.0082</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.6601±0.0120</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.6177±0.0096</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.5244±0.0102</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.6993±0.0121</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.7116±0.0102</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.7406±0.0101</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.7864±0.0098</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.6666±0.0055</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.6626±0.0081</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.6507±0.0071</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.6072±0.0072</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.8049±0.0051</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.7969±0.0069</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.7745±0.0065</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.7090±0.0072</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.5637±0.0060</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.5553±0.0096</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.5329±0.0092</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.4701±0.0086</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.4260±0.0098</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.4275±0.0111</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.4390±0.0100</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.4427±0.0082</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.5868±0.0329</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.5418±0.0328</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.4522±0.0206</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.3710±0.0104</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.4372±0.0097</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.4506±0.0084</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.4892±0.0101</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.5623±0.0113</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9999±0.0004</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.9998±0.0007</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.9982±0.0024</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.6809±0.0061</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.6762±0.0086</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.6625±0.0076</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.6191±0.0070</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.6742±0.0088</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.6537±0.0129</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.6061±0.0101</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.5137±0.0101</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.6880±0.0117</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.7006±0.0101</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.7306±0.0120</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.7792±0.0091</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.2139±0.0209</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.1768±0.0204</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.1087±0.0158</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.0215±0.0090</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.2139±0.0209</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.1768±0.0204</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.1087±0.0158</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0215±0.0090</t>
         </is>
